--- a/Utility Apps/sus_games.xlsx
+++ b/Utility Apps/sus_games.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bibliotecas\Others\GitHub\choukpop-games-saves\Others Games\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bibliotecas\Others\GitHub\choukpop-games-saves\Utility Apps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3D5E64-6B83-4B96-9520-9A23276D9D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BB7582-DFDE-47C2-AB07-E50BB910EA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{55B53CC1-3BC9-426B-9D19-8A523B244D70}"/>
   </bookViews>
@@ -259,7 +259,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -278,14 +278,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -346,15 +338,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -684,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{693509F8-94DF-450D-B39D-62EDCB63AB16}">
-  <dimension ref="B1:D30"/>
+  <dimension ref="B1:D17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="60.7109375" customWidth="1"/>
@@ -851,72 +854,15 @@
       <c r="C17" s="2"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="3"/>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="D1 D31:D1048576">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>"http"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{FF6E694D-2A73-4523-A36E-2B5A748E3050}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Utility Apps/sus_games.xlsx
+++ b/Utility Apps/sus_games.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bibliotecas\Others\GitHub\choukpop-games-saves\Utility Apps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BB7582-DFDE-47C2-AB07-E50BB910EA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D41C503-8130-47CA-95ED-F843D7147525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{55B53CC1-3BC9-426B-9D19-8A523B244D70}"/>
+    <workbookView xWindow="4800" yWindow="1515" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{55B53CC1-3BC9-426B-9D19-8A523B244D70}"/>
   </bookViews>
   <sheets>
     <sheet name="+18 games Favorites" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
   <si>
     <t>Name</t>
   </si>
@@ -99,9 +99,6 @@
     <t>https://f95zone.to/threads/my-best-deal-v4-7-pirot-king.37164/</t>
   </si>
   <si>
-    <t>4.5.5</t>
-  </si>
-  <si>
     <t>0.14</t>
   </si>
   <si>
@@ -180,9 +177,6 @@
     <t>https://f95zone.to/threads/being-a-dik-v0-12-2-9-drpinkcake.25332/</t>
   </si>
   <si>
-    <t>0.11.1</t>
-  </si>
-  <si>
     <t>9.01 Extra</t>
   </si>
   <si>
@@ -253,6 +247,21 @@
   </si>
   <si>
     <t>https://f95zone.to/threads/milfy-city-v1-0e-icstor.8012/</t>
+  </si>
+  <si>
+    <t>0.12.1</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Abandoned</t>
+  </si>
+  <si>
+    <t>Active / no Tag</t>
+  </si>
+  <si>
+    <t>4.5.5 &gt; 4.7</t>
   </si>
 </sst>
 </file>
@@ -288,7 +297,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -298,6 +307,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -330,7 +357,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -339,6 +366,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -687,172 +723,183 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{693509F8-94DF-450D-B39D-62EDCB63AB16}">
-  <dimension ref="B1:D17"/>
+  <dimension ref="B1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="60.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="60.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="40.7109375" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="6" max="6" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:6" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="5" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="6" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+      <c r="F6" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+      <c r="F7" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="E8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="2" t="s">
+    <row r="9" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+      <c r="F9" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+      <c r="F10" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+      <c r="F11" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D12" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+      <c r="F12" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    </row>
+    <row r="14" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="3"/>
+    <row r="15" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1 D31:D1048576">
@@ -861,7 +908,17 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{FF6E694D-2A73-4523-A36E-2B5A748E3050}"/>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{B4F61748-2607-4C36-A434-5434BF8E811C}"/>
+    <hyperlink ref="F11" r:id="rId2" xr:uid="{EA59D677-526B-4964-9B26-8C7234A67D99}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{56E6E6A0-3C82-4CDB-990D-60E2DF47D0BC}"/>
+    <hyperlink ref="F6" r:id="rId4" xr:uid="{C92D8036-8D52-4D46-B4F8-C334EEBBC238}"/>
+    <hyperlink ref="F4" r:id="rId5" xr:uid="{C0FF474F-B968-4993-8747-D009E4EBECA1}"/>
+    <hyperlink ref="F5" r:id="rId6" xr:uid="{87AD82FA-3F37-4D14-BCBC-D8549BC09B3F}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{CEFB4CA2-B74F-4396-8607-42CF7754B530}"/>
+    <hyperlink ref="F9" r:id="rId8" xr:uid="{1D385C68-8C47-4AB7-B6A6-00D331167F22}"/>
+    <hyperlink ref="F10" r:id="rId9" xr:uid="{84B6E560-3C82-4601-923B-EDC2E8BFB954}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{3BDB6F68-659F-431B-973D-1CFD7A5747A6}"/>
+    <hyperlink ref="F13" r:id="rId11" xr:uid="{67C1D6F1-22F1-4C2D-81B7-766C9F44B105}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -869,166 +926,186 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998EE019-872A-4342-BED3-EC62811F404F}">
-  <dimension ref="B1:D16"/>
+  <dimension ref="B1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="60.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="60.7109375" customWidth="1"/>
-    <col min="6" max="6" width="74.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="40.7109375" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="6" max="6" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:6" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+      <c r="F8" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="3" t="s">
+    </row>
+    <row r="10" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="3" t="s">
+    </row>
+    <row r="11" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D11" s="6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="3" t="s">
+    </row>
+    <row r="12" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="2" t="s">
+    <row r="13" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="2:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="3"/>
+    </row>
+    <row r="14" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{0952F687-153A-4025-827B-47F2560A8CA2}"/>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{76277985-91CF-4917-A54A-B1FE7413360D}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{B9F568DD-9456-4FEA-8372-354F92989851}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{51AFDAF9-BD41-48B9-B261-5734124045EA}"/>
+    <hyperlink ref="F6" r:id="rId4" xr:uid="{A4F797FF-A461-4CCB-BA6A-4A3D2BACF07C}"/>
+    <hyperlink ref="F7" r:id="rId5" xr:uid="{5B3B202C-7F93-404B-9E24-A74C5D45AAB7}"/>
+    <hyperlink ref="F8" r:id="rId6" xr:uid="{7BFDE2DF-9D17-42AE-9BF0-FFF99EE920A3}"/>
+    <hyperlink ref="F9" r:id="rId7" xr:uid="{A6A05001-8D0A-49D8-BC65-6AE741134409}"/>
+    <hyperlink ref="F10" r:id="rId8" xr:uid="{0BC05DB2-F7C3-464D-B9A8-8D588A137802}"/>
+    <hyperlink ref="F11" r:id="rId9" xr:uid="{DCB974C3-0E05-418D-8B22-13154C1E71D5}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{E636E5FB-6FF4-4B2A-A0E4-6804A4D45F51}"/>
+    <hyperlink ref="F13" r:id="rId11" xr:uid="{1CC2D09A-B9A5-4C64-B012-A7173880BDFF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Utility Apps/sus_games.xlsx
+++ b/Utility Apps/sus_games.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bibliotecas\Others\GitHub\choukpop-games-saves\Utility Apps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D41C503-8130-47CA-95ED-F843D7147525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79C6AC6-EA8F-4B53-B465-9CFF1FBD9A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="1515" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{55B53CC1-3BC9-426B-9D19-8A523B244D70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{55B53CC1-3BC9-426B-9D19-8A523B244D70}"/>
   </bookViews>
   <sheets>
     <sheet name="+18 games Favorites" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="95">
   <si>
     <t>Name</t>
   </si>
@@ -261,7 +261,67 @@
     <t>Active / no Tag</t>
   </si>
   <si>
-    <t>4.5.5 &gt; 4.7</t>
+    <t xml:space="preserve"> 4.7</t>
+  </si>
+  <si>
+    <t>Saves</t>
+  </si>
+  <si>
+    <t>Mods</t>
+  </si>
+  <si>
+    <t>Need Save</t>
+  </si>
+  <si>
+    <t>No Need Save</t>
+  </si>
+  <si>
+    <t>Multi Mod, Walkthrough Mod, Gallery Unlocker</t>
+  </si>
+  <si>
+    <t>Multi Mod, Walkthrough Mod, Gallery Unlocker, Incest</t>
+  </si>
+  <si>
+    <t>BackDoorConnection</t>
+  </si>
+  <si>
+    <t>GameOfHearts</t>
+  </si>
+  <si>
+    <t>Gallery Unlocker, Incest</t>
+  </si>
+  <si>
+    <t>Walkthrough Mod</t>
+  </si>
+  <si>
+    <t>Multi Mod, Walkthrough Mod, Incest</t>
+  </si>
+  <si>
+    <t>Multi Mod, Walkthrough Mod</t>
+  </si>
+  <si>
+    <t>Incest</t>
+  </si>
+  <si>
+    <t>One</t>
+  </si>
+  <si>
+    <t>Multi Mod, Incest</t>
+  </si>
+  <si>
+    <t>StrandedvSteam</t>
+  </si>
+  <si>
+    <t>Walkthrough inside Game</t>
+  </si>
+  <si>
+    <t>Is Playable?</t>
+  </si>
+  <si>
+    <t>Walkthrough Mod, Gallery Unlocker, Incest</t>
+  </si>
+  <si>
+    <t>Walkthrough Mod, Gallery Unlocker</t>
   </si>
 </sst>
 </file>
@@ -357,7 +417,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -375,6 +435,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -723,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{693509F8-94DF-450D-B39D-62EDCB63AB16}">
-  <dimension ref="B1:F17"/>
+  <dimension ref="B1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.7109375" customWidth="1"/>
@@ -731,10 +794,13 @@
     <col min="4" max="4" width="40.7109375" customWidth="1"/>
     <col min="5" max="5" width="30.7109375" customWidth="1"/>
     <col min="6" max="6" width="60.7109375" customWidth="1"/>
+    <col min="7" max="7" width="40.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:9" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
@@ -744,8 +810,17 @@
       <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>71</v>
       </c>
@@ -758,8 +833,15 @@
       <c r="F3" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>72</v>
       </c>
@@ -772,8 +854,15 @@
       <c r="F4" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G4" s="7"/>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>73</v>
       </c>
@@ -786,8 +875,15 @@
       <c r="F5" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" s="4" t="s">
         <v>47</v>
       </c>
@@ -797,8 +893,18 @@
       <c r="F6" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="D7" s="4" t="s">
         <v>50</v>
       </c>
@@ -808,8 +914,18 @@
       <c r="F7" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G7" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D8" s="4" t="s">
         <v>52</v>
       </c>
@@ -819,8 +935,17 @@
       <c r="F8" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D9" s="5" t="s">
         <v>56</v>
       </c>
@@ -830,8 +955,18 @@
       <c r="F9" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="D10" s="6" t="s">
         <v>59</v>
       </c>
@@ -841,8 +976,17 @@
       <c r="F10" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D11" s="4" t="s">
         <v>62</v>
       </c>
@@ -852,8 +996,15 @@
       <c r="F11" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D12" s="5" t="s">
         <v>65</v>
       </c>
@@ -863,8 +1014,15 @@
       <c r="F12" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D13" s="4" t="s">
         <v>68</v>
       </c>
@@ -874,8 +1032,15 @@
       <c r="F13" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D14" s="4" t="s">
         <v>3</v>
       </c>
@@ -885,21 +1050,37 @@
       <c r="F14" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G14" s="2"/>
+      <c r="H14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="3"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1 D31:D1048576">
@@ -926,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998EE019-872A-4342-BED3-EC62811F404F}">
-  <dimension ref="B1:F16"/>
+  <dimension ref="B1:I16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.7109375" customWidth="1"/>
@@ -934,10 +1115,13 @@
     <col min="4" max="4" width="40.7109375" customWidth="1"/>
     <col min="5" max="5" width="30.7109375" customWidth="1"/>
     <col min="6" max="6" width="60.7109375" customWidth="1"/>
+    <col min="7" max="7" width="40.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:9" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
@@ -947,8 +1131,17 @@
       <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>71</v>
       </c>
@@ -961,8 +1154,15 @@
       <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>72</v>
       </c>
@@ -975,8 +1175,15 @@
       <c r="F4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>73</v>
       </c>
@@ -989,8 +1196,15 @@
       <c r="F5" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
@@ -1000,8 +1214,18 @@
       <c r="F6" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="D7" s="6" t="s">
         <v>18</v>
       </c>
@@ -1011,8 +1235,18 @@
       <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G7" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
@@ -1022,8 +1256,15 @@
       <c r="F8" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D9" s="6" t="s">
         <v>23</v>
       </c>
@@ -1033,8 +1274,18 @@
       <c r="F9" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="D10" s="6" t="s">
         <v>26</v>
       </c>
@@ -1044,8 +1295,15 @@
       <c r="F10" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D11" s="6" t="s">
         <v>29</v>
       </c>
@@ -1055,8 +1313,15 @@
       <c r="F11" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D12" s="6" t="s">
         <v>33</v>
       </c>
@@ -1066,8 +1331,15 @@
       <c r="F12" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="2:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D13" s="6" t="s">
         <v>35</v>
       </c>
@@ -1077,21 +1349,37 @@
       <c r="F13" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="3"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Utility Apps/sus_games.xlsx
+++ b/Utility Apps/sus_games.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bibliotecas\Others\GitHub\choukpop-games-saves\Utility Apps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79C6AC6-EA8F-4B53-B465-9CFF1FBD9A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D74792-3107-4FB7-BF6A-0692773DB7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{55B53CC1-3BC9-426B-9D19-8A523B244D70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{55B53CC1-3BC9-426B-9D19-8A523B244D70}"/>
   </bookViews>
   <sheets>
     <sheet name="+18 games Favorites" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="100">
   <si>
     <t>Name</t>
   </si>
@@ -322,6 +322,21 @@
   </si>
   <si>
     <t>Walkthrough Mod, Gallery Unlocker</t>
+  </si>
+  <si>
+    <t>FURRY MASSAGE</t>
+  </si>
+  <si>
+    <t>Release</t>
+  </si>
+  <si>
+    <t>Much Bigger Than my Boyfriend</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>https://f95zone.to/threads/much-bigger-than-my-boyfriend-v4-0-nimosgames-mrsweetcuckhold.318034/</t>
   </si>
 </sst>
 </file>
@@ -786,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{693509F8-94DF-450D-B39D-62EDCB63AB16}">
-  <dimension ref="B1:I17"/>
+  <dimension ref="B1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.7109375" customWidth="1"/>
@@ -1059,11 +1074,17 @@
       </c>
     </row>
     <row r="15" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="D15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="F15" s="3"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1081,6 +1102,30 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1 D31:D1048576">
@@ -1107,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998EE019-872A-4342-BED3-EC62811F404F}">
-  <dimension ref="B1:I16"/>
+  <dimension ref="B1:I19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.7109375" customWidth="1"/>
@@ -1357,12 +1402,20 @@
       </c>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3"/>
+    <row r="14" spans="2:9" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1380,6 +1433,30 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="4:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
